--- a/output/laminas_comunales/comunal_i_ingr_mean_a_2021_magallanes.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_mean_a_2021_magallanes.xlsx
@@ -494,7 +494,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -503,94 +503,74 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cabo de Hornos</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>336756.03</v>
+          <t>Laguna Blanca</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Laguna Blanca</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>351098.94</v>
+          <t>Torres del Paine</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Natales</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>317599.75</v>
+          <t>Primavera</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Porvenir</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>405893</v>
+          <t>San Gregorio</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Primavera</t>
+          <t>Porvenir</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Punta Arenas</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>397583.41</v>
+          <t>Río Verde</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Río Verde</t>
+          <t>Punta Arenas</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>San Gregorio</t>
+          <t>Natales</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Timaukel</t>
+          <t>Cabo de Hornos</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Torres del Paine</t>
+          <t>Timaukel</t>
         </is>
       </c>
     </row>
